--- a/db/A7XLK-2201-CommunityService.xlsx
+++ b/db/A7XLK-2201-CommunityService.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10509"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10808"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou/db/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCAEA2AE-CAE0-7648-BF67-4F96644EC262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{900655A1-39CB-C74E-800C-94E4E740B8DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1480" yWindow="6400" windowWidth="36660" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
+    <workbookView xWindow="6960" yWindow="12100" windowWidth="44520" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="81">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -337,6 +337,27 @@
   </si>
   <si>
     <t>空污反應管道 &lt;a href="https://docs.google.com/forms/d/e/1FAIpQLScCA0u53XJRjzfBpjv9Bz4JrYH7D6v5wTtPwyVG_Jni0LK7zA/viewform?fbclid=IwAR3zGTtgLnLm8Hb_T45jnBz9iP_FPes2r1h-Z4-JTZeEkMPWiKw-L1OIwhQ"&gt;空污報馬仔&lt;/a&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>市議員參選人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃偉群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+weichunoffice@gmail.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>意見反饋 &lt;a href="https://docs.google.com/forms/d/e/1FAIpQLSdK3SoKe_yRD1JUCHI3ggD9yAvlG2P-FQDj_sPXIdhe7sG0XA/viewform"&gt;換您說說話&lt;/a&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-221-黃偉群.jpeg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -395,12 +416,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -717,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A569E7E5-CF2A-7E44-B2C2-91A32E7499FF}">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
@@ -728,6 +755,7 @@
     <col min="10" max="10" width="30.1640625" customWidth="1"/>
     <col min="11" max="11" width="26.6640625" customWidth="1"/>
     <col min="12" max="12" width="56" customWidth="1"/>
+    <col min="13" max="13" width="50.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -1033,6 +1061,32 @@
       </c>
       <c r="L10" s="1" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="48">
+      <c r="A11">
+        <v>306</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K11" t="s">
+        <v>80</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="M11" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1054,6 +1108,7 @@
     <hyperlink ref="J2" r:id="rId14" xr:uid="{F72405E6-10DE-5541-AAA9-6CE6B9DBDECE}"/>
     <hyperlink ref="J5" r:id="rId15" xr:uid="{8AB23E67-2D66-1142-B20B-6BFC3646BC7D}"/>
     <hyperlink ref="L5" r:id="rId16" xr:uid="{8772DFC9-4DFB-BF48-B50D-1136E2AD3525}"/>
+    <hyperlink ref="L11" r:id="rId17" display="https://www.facebook.com/linlieling" xr:uid="{6E6F4ABB-4D4F-2448-A84D-A09E5D50759A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-2201-CommunityService.xlsx
+++ b/db/A7XLK-2201-CommunityService.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{900655A1-39CB-C74E-800C-94E4E740B8DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7D3EBA-4E1A-3C40-B438-12A92E8B249E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6960" yWindow="12100" windowWidth="44520" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
+    <workbookView xWindow="0" yWindow="5720" windowWidth="39920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="82">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -173,10 +173,6 @@
   </si>
   <si>
     <t>03-320-7676</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>linlieling@gmail.com ; tycca086@tycc.gov.tw</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -358,6 +354,15 @@
   </si>
   <si>
     <t>fig/A7XLK-221-黃偉群.jpeg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>linlieling@gmail.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+https://www.facebook.com/weichun2022</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -810,25 +815,25 @@
         <v>13</v>
       </c>
       <c r="D2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" t="s">
         <v>47</v>
       </c>
-      <c r="E2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>48</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K2" t="s">
+        <v>62</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="K2" t="s">
-        <v>63</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -842,22 +847,22 @@
         <v>14</v>
       </c>
       <c r="D3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" t="s">
         <v>51</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>52</v>
       </c>
-      <c r="F3" t="s">
-        <v>53</v>
-      </c>
       <c r="J3" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K3" t="s">
+        <v>56</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="K3" t="s">
-        <v>57</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -871,22 +876,22 @@
         <v>15</v>
       </c>
       <c r="D4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" t="s">
         <v>54</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>55</v>
       </c>
-      <c r="F4" t="s">
-        <v>56</v>
-      </c>
       <c r="J4" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -897,25 +902,25 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" t="s">
         <v>68</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>69</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>70</v>
       </c>
-      <c r="F5" t="s">
+      <c r="J5" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" t="s">
+        <v>73</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="K5" t="s">
-        <v>74</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -929,19 +934,19 @@
         <v>18</v>
       </c>
       <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F6" t="s">
         <v>36</v>
       </c>
-      <c r="E6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F6" t="s">
-        <v>37</v>
-      </c>
       <c r="K6" t="s">
+        <v>44</v>
+      </c>
+      <c r="L6" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -967,10 +972,10 @@
         <v>23</v>
       </c>
       <c r="K7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -996,10 +1001,10 @@
         <v>27</v>
       </c>
       <c r="K8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1025,13 +1030,13 @@
         <v>31</v>
       </c>
       <c r="K9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1054,13 +1059,13 @@
         <v>34</v>
       </c>
       <c r="G10" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="K10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="48">
@@ -1071,22 +1076,22 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" t="s">
         <v>76</v>
       </c>
-      <c r="D11" t="s">
+      <c r="G11" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="K11" t="s">
+        <v>79</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="M11" t="s">
         <v>78</v>
-      </c>
-      <c r="K11" t="s">
-        <v>80</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="M11" t="s">
-        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/db/A7XLK-2201-CommunityService.xlsx
+++ b/db/A7XLK-2201-CommunityService.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7D3EBA-4E1A-3C40-B438-12A92E8B249E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF7D9945-0D82-1841-852C-432CBBEBD082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="5720" windowWidth="39920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
+    <workbookView xWindow="5400" yWindow="5840" windowWidth="39920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -84,22 +84,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>里長</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>長庚里</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>樂善里</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>文青里</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>民意代表</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -301,10 +285,6 @@
   </si>
   <si>
     <t>https://www.facebook.com/%E9%95%B7%E5%BA%9A%E9%87%8C%E6%9A%A8%E9%95%B7%E5%BA%9A%E9%86%AB%E8%AD%B7%E7%A4%BE%E5%8D%80-479679115425224/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>文化里</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -363,6 +343,26 @@
   <si>
     <t xml:space="preserve">
 https://www.facebook.com/weichun2022</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>里長</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>長庚里</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>樂善里</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文青里</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文化里</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -771,7 +771,7 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -806,121 +806,121 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="K2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K3" t="s">
         <v>52</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="K3" t="s">
-        <v>56</v>
-      </c>
       <c r="L3" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" t="s">
+        <v>51</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K4" t="s">
         <v>53</v>
       </c>
-      <c r="E4" t="s">
+      <c r="L4" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="F4" t="s">
-        <v>55</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="K4" t="s">
-        <v>57</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K5" t="s">
+        <v>68</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="D5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F5" t="s">
-        <v>70</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="K5" t="s">
-        <v>73</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -928,25 +928,25 @@
         <v>301</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -954,28 +954,28 @@
         <v>302</v>
       </c>
       <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
         <v>16</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -983,28 +983,28 @@
         <v>303</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="K8" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1012,31 +1012,31 @@
         <v>304</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K9" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="M9" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1044,28 +1044,28 @@
         <v>305</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="K10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="48">
@@ -1073,25 +1073,25 @@
         <v>306</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="K11" t="s">
-        <v>79</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="M11" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/db/A7XLK-2201-CommunityService.xlsx
+++ b/db/A7XLK-2201-CommunityService.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10808"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11010"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF7D9945-0D82-1841-852C-432CBBEBD082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F368A8F-5459-ED4B-9B64-2E4FD4754488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5400" yWindow="5840" windowWidth="39920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
+    <workbookView xWindow="2180" yWindow="5720" windowWidth="39920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="90">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -363,6 +363,38 @@
   </si>
   <si>
     <t>文化里</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市林口區仁愛路二段 123號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>f0952588598@gmail.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://m12.maxmac.com.tw/front/bin/ptlist.phtml?Category=100537</t>
+  </si>
+  <si>
+    <t>http://m12.maxmac.com.tw/front/bin/ptlist.phtml?Category=100537</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-221-蔡淑君.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=100003586138208</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>選民服務  &lt;a href="http://m12.maxmac.com.tw/front/bin/cglist.phtml?Category=100543"&gt;選民信箱&lt;/a&gt;, &amp;nbsp;&amp;nbsp;
+林口大小事 &lt;a href="http://m12.maxmac.com.tw/front/bin/ptlist.phtml?Category=107185"&gt;淑君報你知&lt;/a&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2603-8989, 02-2601-4834, 0952-588-598</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -749,7 +781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A569E7E5-CF2A-7E44-B2C2-91A32E7499FF}">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
@@ -1092,6 +1124,41 @@
       </c>
       <c r="M11" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="96">
+      <c r="A12">
+        <v>306</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K12" t="s">
+        <v>86</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1114,6 +1181,9 @@
     <hyperlink ref="J5" r:id="rId15" xr:uid="{8AB23E67-2D66-1142-B20B-6BFC3646BC7D}"/>
     <hyperlink ref="L5" r:id="rId16" xr:uid="{8772DFC9-4DFB-BF48-B50D-1136E2AD3525}"/>
     <hyperlink ref="L11" r:id="rId17" display="https://www.facebook.com/linlieling" xr:uid="{6E6F4ABB-4D4F-2448-A84D-A09E5D50759A}"/>
+    <hyperlink ref="G12" r:id="rId18" xr:uid="{8F2A99B4-EF1A-E44F-A6E9-AF6F76A83C6A}"/>
+    <hyperlink ref="J12" r:id="rId19" xr:uid="{9C48DF42-9132-F74B-AEC6-9B18C373C7B8}"/>
+    <hyperlink ref="L12" r:id="rId20" xr:uid="{FB91E1BC-6602-C147-AC45-5CE751E349BC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-2201-CommunityService.xlsx
+++ b/db/A7XLK-2201-CommunityService.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F368A8F-5459-ED4B-9B64-2E4FD4754488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4BBCB87-B556-CC4C-80CF-E8155825BEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2180" yWindow="5720" windowWidth="39920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
+    <workbookView xWindow="740" yWindow="5720" windowWidth="39920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="91">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -309,10 +309,6 @@
   </si>
   <si>
     <t>fig/A7XLK-221-黃明助.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>空污反應管道 &lt;a href="https://docs.google.com/forms/d/e/1FAIpQLScCA0u53XJRjzfBpjv9Bz4JrYH7D6v5wTtPwyVG_Jni0LK7zA/viewform?fbclid=IwAR3zGTtgLnLm8Hb_T45jnBz9iP_FPes2r1h-Z4-JTZeEkMPWiKw-L1OIwhQ"&gt;空污報馬仔&lt;/a&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -329,10 +325,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>意見反饋 &lt;a href="https://docs.google.com/forms/d/e/1FAIpQLSdK3SoKe_yRD1JUCHI3ggD9yAvlG2P-FQDj_sPXIdhe7sG0XA/viewform"&gt;換您說說話&lt;/a&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>fig/A7XLK-221-黃偉群.jpeg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -375,9 +367,6 @@
   </si>
   <si>
     <t>http://m12.maxmac.com.tw/front/bin/ptlist.phtml?Category=100537</t>
-  </si>
-  <si>
-    <t>http://m12.maxmac.com.tw/front/bin/ptlist.phtml?Category=100537</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -389,12 +378,29 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>選民服務  &lt;a href="http://m12.maxmac.com.tw/front/bin/cglist.phtml?Category=100543"&gt;選民信箱&lt;/a&gt;, &amp;nbsp;&amp;nbsp;
-林口大小事 &lt;a href="http://m12.maxmac.com.tw/front/bin/ptlist.phtml?Category=107185"&gt;淑君報你知&lt;/a&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>02-2603-8989, 02-2601-4834, 0952-588-598</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市議員</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蔡淑君</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>意見反饋: &lt;a href="https://docs.google.com/forms/d/e/1FAIpQLSdK3SoKe_yRD1JUCHI3ggD9yAvlG2P-FQDj_sPXIdhe7sG0XA/viewform"&gt;換您說說話&lt;/a&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>空污反應管道: &lt;a href="https://docs.google.com/forms/d/e/1FAIpQLScCA0u53XJRjzfBpjv9Bz4JrYH7D6v5wTtPwyVG_Jni0LK7zA/viewform?fbclid=IwAR3zGTtgLnLm8Hb_T45jnBz9iP_FPes2r1h-Z4-JTZeEkMPWiKw-L1OIwhQ"&gt;空污報馬仔&lt;/a&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;a href="http://m12.maxmac.com.tw/front/bin/ptlist.phtml?Category=100537"&gt;淑君網站&lt;/a&gt; &amp;nbsp; &amp;nbsp;
+選民服務:  &lt;a href="http://m12.maxmac.com.tw/front/bin/cglist.phtml?Category=100543"&gt;選民信箱&lt;/a&gt;, &amp;nbsp;&amp;nbsp;
+林口大小事: &lt;a href="http://m12.maxmac.com.tw/front/bin/ptlist.phtml?Category=107185"&gt;淑君報你知&lt;/a&gt; </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -453,7 +459,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -465,6 +471,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -841,10 +850,10 @@
         <v>203</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
         <v>42</v>
@@ -873,10 +882,10 @@
         <v>204</v>
       </c>
       <c r="B3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" t="s">
         <v>77</v>
-      </c>
-      <c r="C3" t="s">
-        <v>79</v>
       </c>
       <c r="D3" t="s">
         <v>46</v>
@@ -902,10 +911,10 @@
         <v>205</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
         <v>49</v>
@@ -931,10 +940,10 @@
         <v>206</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
         <v>63</v>
@@ -1068,7 +1077,7 @@
         <v>35</v>
       </c>
       <c r="M9" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1091,7 +1100,7 @@
         <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K10" t="s">
         <v>39</v>
@@ -1108,25 +1117,25 @@
         <v>12</v>
       </c>
       <c r="C11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" t="s">
         <v>70</v>
       </c>
-      <c r="D11" t="s">
+      <c r="G11" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="K11" t="s">
         <v>72</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="L11" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="M11" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="96">
+    <row r="12" spans="1:13" ht="144">
       <c r="A12">
         <v>306</v>
       </c>
@@ -1134,31 +1143,31 @@
         <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" t="s">
+        <v>85</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K12" t="s">
+        <v>83</v>
+      </c>
+      <c r="L12" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F12" t="s">
-        <v>89</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="K12" t="s">
-        <v>86</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="M12" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/db/A7XLK-2201-CommunityService.xlsx
+++ b/db/A7XLK-2201-CommunityService.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4BBCB87-B556-CC4C-80CF-E8155825BEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{879032CD-466D-8E40-8257-246DDC737D80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="740" yWindow="5720" windowWidth="39920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
+    <workbookView xWindow="1540" yWindow="5720" windowWidth="39920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="98">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -401,6 +401,34 @@
     <t xml:space="preserve">&lt;a href="http://m12.maxmac.com.tw/front/bin/ptlist.phtml?Category=100537"&gt;淑君網站&lt;/a&gt; &amp;nbsp; &amp;nbsp;
 選民服務:  &lt;a href="http://m12.maxmac.com.tw/front/bin/cglist.phtml?Category=100543"&gt;選民信箱&lt;/a&gt;, &amp;nbsp;&amp;nbsp;
 林口大小事: &lt;a href="http://m12.maxmac.com.tw/front/bin/ptlist.phtml?Category=107185"&gt;淑君報你知&lt;/a&gt; </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳明義</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市五股區新五路3段228號1樓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2293-5006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mingyi.service@gmail.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/imingyi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://line.me/ti/p/%40ith6286h?fbclid=IwAR0WDLLQaRLb9YdSqvFNQO9ZKfh3z3ifIqQQZtwiwfxldxOnUSPSsoiI3pw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-221-陳明義.jpeg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -790,7 +818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A569E7E5-CF2A-7E44-B2C2-91A32E7499FF}">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
@@ -1137,7 +1165,7 @@
     </row>
     <row r="12" spans="1:13" ht="144">
       <c r="A12">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -1168,6 +1196,38 @@
       </c>
       <c r="M12" s="2" t="s">
         <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13">
+        <v>308</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" t="s">
+        <v>91</v>
+      </c>
+      <c r="E13" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13" t="s">
+        <v>93</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K13" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1193,6 +1253,9 @@
     <hyperlink ref="G12" r:id="rId18" xr:uid="{8F2A99B4-EF1A-E44F-A6E9-AF6F76A83C6A}"/>
     <hyperlink ref="J12" r:id="rId19" xr:uid="{9C48DF42-9132-F74B-AEC6-9B18C373C7B8}"/>
     <hyperlink ref="L12" r:id="rId20" xr:uid="{FB91E1BC-6602-C147-AC45-5CE751E349BC}"/>
+    <hyperlink ref="G13" r:id="rId21" xr:uid="{D969DFE3-72F2-FC46-AF63-BACD51F88111}"/>
+    <hyperlink ref="L13" r:id="rId22" xr:uid="{FD18C2C7-7B94-DD4B-BC68-D2F43975654B}"/>
+    <hyperlink ref="J13" r:id="rId23" xr:uid="{D42849F6-A732-7246-B17A-494F7AADFD90}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-2201-CommunityService.xlsx
+++ b/db/A7XLK-2201-CommunityService.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11010"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10410"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{879032CD-466D-8E40-8257-246DDC737D80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E631A1F2-ED49-7B48-A8F7-28731A47B232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1540" yWindow="5720" windowWidth="39920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
+    <workbookView xWindow="2640" yWindow="3100" windowWidth="30680" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -394,10 +394,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>空污反應管道: &lt;a href="https://docs.google.com/forms/d/e/1FAIpQLScCA0u53XJRjzfBpjv9Bz4JrYH7D6v5wTtPwyVG_Jni0LK7zA/viewform?fbclid=IwAR3zGTtgLnLm8Hb_T45jnBz9iP_FPes2r1h-Z4-JTZeEkMPWiKw-L1OIwhQ"&gt;空污報馬仔&lt;/a&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">&lt;a href="http://m12.maxmac.com.tw/front/bin/ptlist.phtml?Category=100537"&gt;淑君網站&lt;/a&gt; &amp;nbsp; &amp;nbsp;
 選民服務:  &lt;a href="http://m12.maxmac.com.tw/front/bin/cglist.phtml?Category=100543"&gt;選民信箱&lt;/a&gt;, &amp;nbsp;&amp;nbsp;
 林口大小事: &lt;a href="http://m12.maxmac.com.tw/front/bin/ptlist.phtml?Category=107185"&gt;淑君報你知&lt;/a&gt; </t>
@@ -429,6 +425,11 @@
   </si>
   <si>
     <t>fig/A7XLK-221-陳明義.jpeg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>空污反應管道: &lt;a href="https://docs.google.com/forms/d/e/1FAIpQLScCA0u53XJRjzfBpjv9Bz4JrYH7D6v5wTtPwyVG_Jni0LK7zA/viewform?fbclid=IwAR3zGTtgLnLm8Hb_T45jnBz9iP_FPes2r1h-Z4-JTZeEkMPWiKw-L1OIwhQ"&gt;空污報馬仔&lt;/a&gt; &lt;br&gt;
+向市民報告 &lt;a href="https://issuu.com/niuhsuting/docs/220325_"&gt;環保議員 除公害&lt;/a&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1076,7 +1077,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" ht="128">
       <c r="A9">
         <v>304</v>
       </c>
@@ -1104,8 +1105,8 @@
       <c r="L9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="M9" t="s">
-        <v>89</v>
+      <c r="M9" s="2" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1195,7 +1196,7 @@
         <v>84</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1209,25 +1210,25 @@
         <v>86</v>
       </c>
       <c r="D13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E13" t="s">
         <v>91</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>92</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="J13" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K13" t="s">
+        <v>96</v>
+      </c>
+      <c r="L13" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="K13" t="s">
-        <v>97</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/db/A7XLK-2201-CommunityService.xlsx
+++ b/db/A7XLK-2201-CommunityService.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E631A1F2-ED49-7B48-A8F7-28731A47B232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F1CDCF-75CB-B04B-82B8-FB8BED4E635A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="3100" windowWidth="30680" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
+    <workbookView xWindow="880" yWindow="1040" windowWidth="27940" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="99">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -431,6 +431,9 @@
     <t>空污反應管道: &lt;a href="https://docs.google.com/forms/d/e/1FAIpQLScCA0u53XJRjzfBpjv9Bz4JrYH7D6v5wTtPwyVG_Jni0LK7zA/viewform?fbclid=IwAR3zGTtgLnLm8Hb_T45jnBz9iP_FPes2r1h-Z4-JTZeEkMPWiKw-L1OIwhQ"&gt;空污報馬仔&lt;/a&gt; &lt;br&gt;
 向市民報告 &lt;a href="https://issuu.com/niuhsuting/docs/220325_"&gt;環保議員 除公害&lt;/a&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.tpp.org.tw/action/result_content.php?id=58</t>
   </si>
 </sst>
 </file>
@@ -819,7 +822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A569E7E5-CF2A-7E44-B2C2-91A32E7499FF}">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
@@ -1164,44 +1167,36 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="144">
+    <row r="12" spans="1:13">
       <c r="A12">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
+      </c>
+      <c r="D12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" t="s">
+        <v>50</v>
       </c>
       <c r="F12" t="s">
-        <v>85</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>82</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="J12" s="1"/>
       <c r="K12" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="144">
       <c r="A13">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -1209,25 +1204,60 @@
       <c r="C13" t="s">
         <v>86</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K13" t="s">
+        <v>83</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14">
+        <v>308</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" t="s">
         <v>90</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E14" t="s">
         <v>91</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F14" t="s">
         <v>92</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K14" t="s">
         <v>96</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="L14" s="1" t="s">
         <v>94</v>
       </c>
     </row>
@@ -1251,12 +1281,12 @@
     <hyperlink ref="J5" r:id="rId15" xr:uid="{8AB23E67-2D66-1142-B20B-6BFC3646BC7D}"/>
     <hyperlink ref="L5" r:id="rId16" xr:uid="{8772DFC9-4DFB-BF48-B50D-1136E2AD3525}"/>
     <hyperlink ref="L11" r:id="rId17" display="https://www.facebook.com/linlieling" xr:uid="{6E6F4ABB-4D4F-2448-A84D-A09E5D50759A}"/>
-    <hyperlink ref="G12" r:id="rId18" xr:uid="{8F2A99B4-EF1A-E44F-A6E9-AF6F76A83C6A}"/>
-    <hyperlink ref="J12" r:id="rId19" xr:uid="{9C48DF42-9132-F74B-AEC6-9B18C373C7B8}"/>
-    <hyperlink ref="L12" r:id="rId20" xr:uid="{FB91E1BC-6602-C147-AC45-5CE751E349BC}"/>
-    <hyperlink ref="G13" r:id="rId21" xr:uid="{D969DFE3-72F2-FC46-AF63-BACD51F88111}"/>
-    <hyperlink ref="L13" r:id="rId22" xr:uid="{FD18C2C7-7B94-DD4B-BC68-D2F43975654B}"/>
-    <hyperlink ref="J13" r:id="rId23" xr:uid="{D42849F6-A732-7246-B17A-494F7AADFD90}"/>
+    <hyperlink ref="G13" r:id="rId18" xr:uid="{8F2A99B4-EF1A-E44F-A6E9-AF6F76A83C6A}"/>
+    <hyperlink ref="J13" r:id="rId19" xr:uid="{9C48DF42-9132-F74B-AEC6-9B18C373C7B8}"/>
+    <hyperlink ref="L13" r:id="rId20" xr:uid="{FB91E1BC-6602-C147-AC45-5CE751E349BC}"/>
+    <hyperlink ref="G14" r:id="rId21" xr:uid="{D969DFE3-72F2-FC46-AF63-BACD51F88111}"/>
+    <hyperlink ref="L14" r:id="rId22" xr:uid="{FD18C2C7-7B94-DD4B-BC68-D2F43975654B}"/>
+    <hyperlink ref="J14" r:id="rId23" xr:uid="{D42849F6-A732-7246-B17A-494F7AADFD90}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-2201-CommunityService.xlsx
+++ b/db/A7XLK-2201-CommunityService.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F1CDCF-75CB-B04B-82B8-FB8BED4E635A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC82BA43-654D-FE4E-B44F-4F3B7E04C6FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="880" yWindow="1040" windowWidth="27940" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
+    <workbookView xWindow="1540" yWindow="1780" windowWidth="27920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="100">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -434,6 +434,10 @@
   </si>
   <si>
     <t>https://www.tpp.org.tw/action/result_content.php?id=58</t>
+  </si>
+  <si>
+    <t>fig/A7XLK-221-簡僑亨2.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1188,7 +1192,7 @@
       </c>
       <c r="J12" s="1"/>
       <c r="K12" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>98</v>

--- a/db/A7XLK-2201-CommunityService.xlsx
+++ b/db/A7XLK-2201-CommunityService.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10410"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10520"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC82BA43-654D-FE4E-B44F-4F3B7E04C6FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA987A1B-6EC2-A842-9CD0-28CF12752887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1540" yWindow="1780" windowWidth="27920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="27920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="119">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -316,28 +316,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>黃偉群</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-weichunoffice@gmail.com</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/A7XLK-221-黃偉群.jpeg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>linlieling@gmail.com</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">
-https://www.facebook.com/weichun2022</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>里長</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -387,10 +369,6 @@
   </si>
   <si>
     <t>蔡淑君</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>意見反饋: &lt;a href="https://docs.google.com/forms/d/e/1FAIpQLSdK3SoKe_yRD1JUCHI3ggD9yAvlG2P-FQDj_sPXIdhe7sG0XA/viewform"&gt;換您說說話&lt;/a&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -437,6 +415,101 @@
   </si>
   <si>
     <t>fig/A7XLK-221-簡僑亨2.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>市議員&amp;參選人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>party</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>民進黨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>無黨籍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>民眾黨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>國民黨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>孫韻璇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林明義</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李宗豪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/TYleehao</t>
+  </si>
+  <si>
+    <t>Tyleehao2022@gmail.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-221-李宗豪.jpeg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/stephine3206763</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-211-孫韻璇.jpeg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/people/%E9%BE%9C%E5%B1%B1%E5%8D%80%E5%A4%A7%E5%90%8C%E9%87%8C%E8%BE%A6%E5%85%AC%E8%99%95-%E9%87%8C%E9%95%B7-%E6%9E%97%E6%98%8E%E7%BE%A9/100064226881669/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龜山區大同路127號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-320-0962</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-211-林明義.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>現任: 龜山區文青里 里長</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>現任: 龜山區大同里 里長</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>現任: 龜山區議員林俐玲特助 (林議員之子)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龜山區光峯路千禧新城141號1樓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-320-6763</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>現任: 龜山區精忠里 里長</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -495,7 +568,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -503,9 +576,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
@@ -826,21 +896,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A569E7E5-CF2A-7E44-B2C2-91A32E7499FF}">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" customWidth="1"/>
-    <col min="5" max="5" width="28.5" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" customWidth="1"/>
-    <col min="7" max="7" width="19.5" customWidth="1"/>
-    <col min="10" max="10" width="30.1640625" customWidth="1"/>
-    <col min="11" max="11" width="26.6640625" customWidth="1"/>
-    <col min="12" max="12" width="56" customWidth="1"/>
-    <col min="13" max="13" width="50.6640625" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="5" width="7.6640625" customWidth="1"/>
+    <col min="6" max="6" width="28.5" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" customWidth="1"/>
+    <col min="8" max="8" width="19.5" customWidth="1"/>
+    <col min="11" max="11" width="30.1640625" customWidth="1"/>
+    <col min="12" max="12" width="26.6640625" customWidth="1"/>
+    <col min="13" max="13" width="56" customWidth="1"/>
+    <col min="14" max="14" width="50.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -854,443 +925,553 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2">
         <v>203</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
         <v>42</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>60</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>43</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>58</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="A3">
         <v>204</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
         <v>46</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>47</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>48</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>52</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:14">
       <c r="A4">
         <v>205</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
         <v>49</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>50</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>51</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>53</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:14">
       <c r="A5">
         <v>206</v>
       </c>
       <c r="B5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" t="s">
         <v>75</v>
-      </c>
-      <c r="C5" t="s">
-        <v>79</v>
       </c>
       <c r="D5" t="s">
         <v>63</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>64</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>65</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>68</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:14">
       <c r="A6">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6" t="s">
-        <v>40</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>17</v>
+      </c>
+      <c r="G6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" t="s">
+        <v>37</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K7" t="s">
-        <v>37</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>29</v>
+      </c>
+      <c r="G7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L7" t="s">
+        <v>106</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8" t="s">
-        <v>38</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="128">
+        <v>116</v>
+      </c>
+      <c r="G8" t="s">
+        <v>117</v>
+      </c>
+      <c r="H8" s="1"/>
+      <c r="L8" t="s">
+        <v>108</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="N8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="K9" t="s">
-        <v>59</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>110</v>
+      </c>
+      <c r="G9" t="s">
+        <v>111</v>
+      </c>
+      <c r="H9" s="1"/>
+      <c r="L9" t="s">
+        <v>112</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="N9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10">
-        <v>305</v>
+        <v>331</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="F10" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G10" t="s">
-        <v>73</v>
-      </c>
-      <c r="K10" t="s">
-        <v>39</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="48">
+        <v>51</v>
+      </c>
+      <c r="K10" s="1"/>
+      <c r="L10" t="s">
+        <v>94</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="N10" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="128">
       <c r="A11">
-        <v>306</v>
+        <v>341</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="K11" t="s">
-        <v>72</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="M11" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
+        <v>98</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12">
-        <v>309</v>
+        <v>401</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
-      </c>
-      <c r="J12" s="1"/>
-      <c r="K12" t="s">
-        <v>99</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="144">
+        <v>61</v>
+      </c>
+      <c r="G12" t="s">
+        <v>32</v>
+      </c>
+      <c r="L12" t="s">
+        <v>40</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13">
-        <v>307</v>
+        <v>402</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>80</v>
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" t="s">
+        <v>100</v>
       </c>
       <c r="F13" t="s">
-        <v>85</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="K13" t="s">
-        <v>83</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+        <v>21</v>
+      </c>
+      <c r="G13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L13" t="s">
+        <v>38</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14">
-        <v>308</v>
+        <v>403</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" t="s">
+        <v>97</v>
+      </c>
+      <c r="F14" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" t="s">
+        <v>70</v>
+      </c>
+      <c r="L14" t="s">
+        <v>39</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="144">
+      <c r="A15">
+        <v>405</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" t="s">
+        <v>81</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L15" t="s">
+        <v>79</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16">
+        <v>406</v>
+      </c>
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" t="s">
+        <v>100</v>
+      </c>
+      <c r="F16" t="s">
         <v>86</v>
       </c>
-      <c r="D14" t="s">
+      <c r="G16" t="s">
+        <v>87</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E14" t="s">
+      <c r="L16" t="s">
         <v>91</v>
       </c>
-      <c r="F14" t="s">
-        <v>92</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="K14" t="s">
-        <v>96</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>94</v>
+      <c r="M16" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N16">
+    <sortCondition ref="A2:A16"/>
+  </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G7" r:id="rId1" xr:uid="{6761C840-3BCE-E546-851A-F942ACFB5A27}"/>
-    <hyperlink ref="G8" r:id="rId2" xr:uid="{54F4D35F-E2E2-C842-A43F-1D511AA423E2}"/>
-    <hyperlink ref="G9" r:id="rId3" xr:uid="{DACA889F-BEB8-EB44-9F74-8DADCD28AC1A}"/>
-    <hyperlink ref="L7" r:id="rId4" xr:uid="{D91A9473-C470-1C4A-BCC7-538AC623916D}"/>
-    <hyperlink ref="L8" r:id="rId5" xr:uid="{F2F6C49C-3706-8849-A592-2D557E4E0729}"/>
-    <hyperlink ref="L9" r:id="rId6" xr:uid="{66AA02E1-FFD6-BD40-9BF8-43E5847A592E}"/>
-    <hyperlink ref="L10" r:id="rId7" xr:uid="{70BEFD60-7B6E-D74B-BFFF-FC1C55DB4DC8}"/>
-    <hyperlink ref="L6" r:id="rId8" xr:uid="{3156EB90-5C6B-AE46-BC4D-1028A6B5CA40}"/>
-    <hyperlink ref="L2" r:id="rId9" xr:uid="{F79F65C5-A7F1-394D-841F-F98A2C79B07E}"/>
-    <hyperlink ref="L4" r:id="rId10" xr:uid="{31B25D2E-7FCD-BC4A-948B-6E4C67219F72}"/>
-    <hyperlink ref="J4" r:id="rId11" xr:uid="{0F950778-B761-374A-AF83-311F0B6581CF}"/>
-    <hyperlink ref="J3" r:id="rId12" xr:uid="{BA95A22C-8329-854A-B21A-08BE7A9E0A3D}"/>
-    <hyperlink ref="L3" r:id="rId13" xr:uid="{D0EE2661-AC9C-0841-8EFD-47FEA6E05264}"/>
-    <hyperlink ref="J2" r:id="rId14" xr:uid="{F72405E6-10DE-5541-AAA9-6CE6B9DBDECE}"/>
-    <hyperlink ref="J5" r:id="rId15" xr:uid="{8AB23E67-2D66-1142-B20B-6BFC3646BC7D}"/>
-    <hyperlink ref="L5" r:id="rId16" xr:uid="{8772DFC9-4DFB-BF48-B50D-1136E2AD3525}"/>
-    <hyperlink ref="L11" r:id="rId17" display="https://www.facebook.com/linlieling" xr:uid="{6E6F4ABB-4D4F-2448-A84D-A09E5D50759A}"/>
-    <hyperlink ref="G13" r:id="rId18" xr:uid="{8F2A99B4-EF1A-E44F-A6E9-AF6F76A83C6A}"/>
-    <hyperlink ref="J13" r:id="rId19" xr:uid="{9C48DF42-9132-F74B-AEC6-9B18C373C7B8}"/>
-    <hyperlink ref="L13" r:id="rId20" xr:uid="{FB91E1BC-6602-C147-AC45-5CE751E349BC}"/>
-    <hyperlink ref="G14" r:id="rId21" xr:uid="{D969DFE3-72F2-FC46-AF63-BACD51F88111}"/>
-    <hyperlink ref="L14" r:id="rId22" xr:uid="{FD18C2C7-7B94-DD4B-BC68-D2F43975654B}"/>
-    <hyperlink ref="J14" r:id="rId23" xr:uid="{D42849F6-A732-7246-B17A-494F7AADFD90}"/>
+    <hyperlink ref="H13" r:id="rId1" xr:uid="{54F4D35F-E2E2-C842-A43F-1D511AA423E2}"/>
+    <hyperlink ref="M13" r:id="rId2" xr:uid="{F2F6C49C-3706-8849-A592-2D557E4E0729}"/>
+    <hyperlink ref="M14" r:id="rId3" xr:uid="{70BEFD60-7B6E-D74B-BFFF-FC1C55DB4DC8}"/>
+    <hyperlink ref="M12" r:id="rId4" xr:uid="{3156EB90-5C6B-AE46-BC4D-1028A6B5CA40}"/>
+    <hyperlink ref="M2" r:id="rId5" xr:uid="{F79F65C5-A7F1-394D-841F-F98A2C79B07E}"/>
+    <hyperlink ref="M4" r:id="rId6" xr:uid="{31B25D2E-7FCD-BC4A-948B-6E4C67219F72}"/>
+    <hyperlink ref="K4" r:id="rId7" xr:uid="{0F950778-B761-374A-AF83-311F0B6581CF}"/>
+    <hyperlink ref="K3" r:id="rId8" xr:uid="{BA95A22C-8329-854A-B21A-08BE7A9E0A3D}"/>
+    <hyperlink ref="M3" r:id="rId9" xr:uid="{D0EE2661-AC9C-0841-8EFD-47FEA6E05264}"/>
+    <hyperlink ref="K2" r:id="rId10" xr:uid="{F72405E6-10DE-5541-AAA9-6CE6B9DBDECE}"/>
+    <hyperlink ref="K5" r:id="rId11" xr:uid="{8AB23E67-2D66-1142-B20B-6BFC3646BC7D}"/>
+    <hyperlink ref="M5" r:id="rId12" xr:uid="{8772DFC9-4DFB-BF48-B50D-1136E2AD3525}"/>
+    <hyperlink ref="H15" r:id="rId13" xr:uid="{8F2A99B4-EF1A-E44F-A6E9-AF6F76A83C6A}"/>
+    <hyperlink ref="K15" r:id="rId14" xr:uid="{9C48DF42-9132-F74B-AEC6-9B18C373C7B8}"/>
+    <hyperlink ref="M15" r:id="rId15" xr:uid="{FB91E1BC-6602-C147-AC45-5CE751E349BC}"/>
+    <hyperlink ref="H16" r:id="rId16" xr:uid="{D969DFE3-72F2-FC46-AF63-BACD51F88111}"/>
+    <hyperlink ref="M16" r:id="rId17" xr:uid="{FD18C2C7-7B94-DD4B-BC68-D2F43975654B}"/>
+    <hyperlink ref="K16" r:id="rId18" xr:uid="{D42849F6-A732-7246-B17A-494F7AADFD90}"/>
+    <hyperlink ref="H11" r:id="rId19" xr:uid="{AE3EABA0-3E8F-4641-AC13-47FAE0871412}"/>
+    <hyperlink ref="M11" r:id="rId20" xr:uid="{CCA37CD9-E904-FF41-9A63-795B604A0EDA}"/>
+    <hyperlink ref="H6" r:id="rId21" xr:uid="{8B2ABF59-6A09-D64E-A36C-82801EF3A6B8}"/>
+    <hyperlink ref="M6" r:id="rId22" xr:uid="{A5ACDF0B-E628-7647-8966-0C1587EC2DB0}"/>
+    <hyperlink ref="H7" r:id="rId23" xr:uid="{61BDCF0F-F4AD-784C-9848-84763C44F36B}"/>
+    <hyperlink ref="M8" r:id="rId24" xr:uid="{58F61CBD-EA6F-1341-B53F-4365AFEC1F31}"/>
+    <hyperlink ref="M9" r:id="rId25" xr:uid="{7D28E37E-5F6A-A947-A8C2-C1F4DEA478F1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-2201-CommunityService.xlsx
+++ b/db/A7XLK-2201-CommunityService.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA987A1B-6EC2-A842-9CD0-28CF12752887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDF873BF-8A25-0A42-8AFC-64E3760C2D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="27920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
   </bookViews>
@@ -465,10 +465,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.facebook.com/stephine3206763</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>fig/A7XLK-211-孫韻璇.jpeg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -510,6 +506,10 @@
   </si>
   <si>
     <t>現任: 龜山區精忠里 里長</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/sun0976315743</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1138,7 +1138,7 @@
         <v>104</v>
       </c>
       <c r="N7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1158,20 +1158,20 @@
         <v>100</v>
       </c>
       <c r="F8" t="s">
+        <v>115</v>
+      </c>
+      <c r="G8" t="s">
         <v>116</v>
-      </c>
-      <c r="G8" t="s">
-        <v>117</v>
       </c>
       <c r="H8" s="1"/>
       <c r="L8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="N8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1191,20 +1191,20 @@
         <v>100</v>
       </c>
       <c r="F9" t="s">
+        <v>109</v>
+      </c>
+      <c r="G9" t="s">
         <v>110</v>
-      </c>
-      <c r="G9" t="s">
-        <v>111</v>
       </c>
       <c r="H9" s="1"/>
       <c r="L9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1237,7 +1237,7 @@
         <v>93</v>
       </c>
       <c r="N10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="128">

--- a/db/A7XLK-2201-CommunityService.xlsx
+++ b/db/A7XLK-2201-CommunityService.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDF873BF-8A25-0A42-8AFC-64E3760C2D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D72CB21F-382B-BA43-8DB5-10BCE337B813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="27920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
   </bookViews>
@@ -481,10 +481,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>fig/A7XLK-211-林明義.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>現任: 龜山區文青里 里長</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -510,6 +506,10 @@
   </si>
   <si>
     <t>https://www.facebook.com/sun0976315743</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-211-林明義-02.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1138,7 +1138,7 @@
         <v>104</v>
       </c>
       <c r="N7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1158,20 +1158,20 @@
         <v>100</v>
       </c>
       <c r="F8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G8" t="s">
         <v>115</v>
-      </c>
-      <c r="G8" t="s">
-        <v>116</v>
       </c>
       <c r="H8" s="1"/>
       <c r="L8" t="s">
         <v>107</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1198,13 +1198,13 @@
       </c>
       <c r="H9" s="1"/>
       <c r="L9" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>108</v>
       </c>
       <c r="N9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1237,7 +1237,7 @@
         <v>93</v>
       </c>
       <c r="N10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="128">

--- a/db/A7XLK-2201-CommunityService.xlsx
+++ b/db/A7XLK-2201-CommunityService.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D72CB21F-382B-BA43-8DB5-10BCE337B813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A6EA3D-74F3-2348-9DF4-8898A9E72014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="27920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
   </bookViews>
@@ -168,10 +168,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.facebook.com/profile.php?id=2141577432747856</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://www.facebook.com/profile.php?id=100008316096117</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -510,6 +506,10 @@
   </si>
   <si>
     <t>fig/A7XLK-211-林明義-02.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=100063574997048</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -925,7 +925,7 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -960,31 +960,31 @@
         <v>203</v>
       </c>
       <c r="B2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" t="s">
         <v>71</v>
       </c>
-      <c r="C2" t="s">
-        <v>72</v>
-      </c>
       <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G2" t="s">
         <v>42</v>
       </c>
-      <c r="F2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>43</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L2" t="s">
-        <v>58</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -992,28 +992,28 @@
         <v>204</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" t="s">
         <v>46</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>47</v>
       </c>
-      <c r="G3" t="s">
-        <v>48</v>
-      </c>
       <c r="K3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L3" t="s">
+        <v>51</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="L3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1021,28 +1021,28 @@
         <v>205</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" t="s">
         <v>49</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>50</v>
       </c>
-      <c r="G4" t="s">
-        <v>51</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1050,28 +1050,28 @@
         <v>206</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" t="s">
         <v>63</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>64</v>
       </c>
-      <c r="G5" t="s">
+      <c r="K5" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" t="s">
+        <v>67</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="L5" t="s">
-        <v>68</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1082,13 +1082,13 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F6" t="s">
         <v>17</v>
@@ -1100,10 +1100,10 @@
         <v>19</v>
       </c>
       <c r="L6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>33</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1114,13 +1114,13 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F7" t="s">
         <v>29</v>
@@ -1129,16 +1129,16 @@
         <v>30</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="L7" t="s">
         <v>105</v>
       </c>
-      <c r="L7" t="s">
-        <v>106</v>
-      </c>
       <c r="M7" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1149,29 +1149,29 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G8" t="s">
         <v>114</v>
-      </c>
-      <c r="G8" t="s">
-        <v>115</v>
       </c>
       <c r="H8" s="1"/>
       <c r="L8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1182,29 +1182,29 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F9" t="s">
+        <v>108</v>
+      </c>
+      <c r="G9" t="s">
         <v>109</v>
-      </c>
-      <c r="G9" t="s">
-        <v>110</v>
       </c>
       <c r="H9" s="1"/>
       <c r="L9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1215,29 +1215,29 @@
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F10" t="s">
         <v>49</v>
       </c>
-      <c r="E10" t="s">
-        <v>99</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>50</v>
-      </c>
-      <c r="G10" t="s">
-        <v>51</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="128">
@@ -1248,13 +1248,13 @@
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F11" t="s">
         <v>25</v>
@@ -1266,13 +1266,13 @@
         <v>27</v>
       </c>
       <c r="L11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1289,19 +1289,19 @@
         <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G12" t="s">
         <v>32</v>
       </c>
       <c r="L12" t="s">
+        <v>39</v>
+      </c>
+      <c r="M12" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1318,7 +1318,7 @@
         <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1330,10 +1330,10 @@
         <v>23</v>
       </c>
       <c r="L13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1350,7 +1350,7 @@
         <v>28</v>
       </c>
       <c r="E14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F14" t="s">
         <v>29</v>
@@ -1359,13 +1359,13 @@
         <v>30</v>
       </c>
       <c r="H14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="144">
@@ -1376,34 +1376,34 @@
         <v>12</v>
       </c>
       <c r="C15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" t="s">
+        <v>80</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="L15" t="s">
+        <v>78</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G15" t="s">
-        <v>81</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="L15" t="s">
-        <v>79</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1414,31 +1414,31 @@
         <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" t="s">
+        <v>99</v>
+      </c>
+      <c r="F16" t="s">
         <v>85</v>
       </c>
-      <c r="E16" t="s">
-        <v>100</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>86</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="K16" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="L16" t="s">
+        <v>90</v>
+      </c>
+      <c r="M16" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="L16" t="s">
-        <v>91</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/db/A7XLK-2201-CommunityService.xlsx
+++ b/db/A7XLK-2201-CommunityService.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A6EA3D-74F3-2348-9DF4-8898A9E72014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD7774F-7A0F-8241-BCC3-082C71C25DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="27920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
+    <workbookView xWindow="3980" yWindow="-19820" windowWidth="27920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="126">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -510,6 +510,34 @@
   </si>
   <si>
     <t>https://www.facebook.com/profile.php?id=100063574997048</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/LAG555</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳泓維</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>現任: 立委賴香伶桃園辦公室 主任</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區中興路</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0937-121-555</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chwlag@gmail.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-221-陳泓維.jpeg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -896,7 +924,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A569E7E5-CF2A-7E44-B2C2-91A32E7499FF}">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
@@ -1240,105 +1268,109 @@
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="128">
+    <row r="11" spans="1:14" ht="16">
       <c r="A11">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="E11" t="s">
-        <v>97</v>
-      </c>
-      <c r="F11" t="s">
-        <v>25</v>
+        <v>98</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="G11" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>27</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="K11" s="1"/>
       <c r="L11" t="s">
-        <v>58</v>
+        <v>125</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>119</v>
+      </c>
+      <c r="N11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="128">
       <c r="A12">
-        <v>401</v>
+        <v>341</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="G12" t="s">
-        <v>32</v>
+        <v>26</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="L12" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E13" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F13" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="G13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="L13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -1347,68 +1379,62 @@
         <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F14" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G14" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14" t="s">
-        <v>69</v>
+        <v>22</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="144">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>75</v>
+        <v>15</v>
+      </c>
+      <c r="D15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" t="s">
+        <v>96</v>
+      </c>
+      <c r="F15" t="s">
+        <v>29</v>
       </c>
       <c r="G15" t="s">
-        <v>80</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>77</v>
+        <v>30</v>
+      </c>
+      <c r="H15" t="s">
+        <v>69</v>
       </c>
       <c r="L15" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="144">
       <c r="A16">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
@@ -1416,41 +1442,79 @@
       <c r="C16" t="s">
         <v>81</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" t="s">
+        <v>80</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="L16" t="s">
+        <v>78</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17">
+        <v>406</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" t="s">
         <v>84</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E17" t="s">
         <v>99</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F17" t="s">
         <v>85</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G17" t="s">
         <v>86</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="K17" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="L16" t="s">
+      <c r="L17" t="s">
         <v>90</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="M17" s="1" t="s">
         <v>88</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N16">
-    <sortCondition ref="A2:A16"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N17">
+    <sortCondition ref="A2:A17"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="H13" r:id="rId1" xr:uid="{54F4D35F-E2E2-C842-A43F-1D511AA423E2}"/>
-    <hyperlink ref="M13" r:id="rId2" xr:uid="{F2F6C49C-3706-8849-A592-2D557E4E0729}"/>
-    <hyperlink ref="M14" r:id="rId3" xr:uid="{70BEFD60-7B6E-D74B-BFFF-FC1C55DB4DC8}"/>
-    <hyperlink ref="M12" r:id="rId4" xr:uid="{3156EB90-5C6B-AE46-BC4D-1028A6B5CA40}"/>
+    <hyperlink ref="H14" r:id="rId1" xr:uid="{54F4D35F-E2E2-C842-A43F-1D511AA423E2}"/>
+    <hyperlink ref="M14" r:id="rId2" xr:uid="{F2F6C49C-3706-8849-A592-2D557E4E0729}"/>
+    <hyperlink ref="M15" r:id="rId3" xr:uid="{70BEFD60-7B6E-D74B-BFFF-FC1C55DB4DC8}"/>
+    <hyperlink ref="M13" r:id="rId4" xr:uid="{3156EB90-5C6B-AE46-BC4D-1028A6B5CA40}"/>
     <hyperlink ref="M2" r:id="rId5" xr:uid="{F79F65C5-A7F1-394D-841F-F98A2C79B07E}"/>
     <hyperlink ref="M4" r:id="rId6" xr:uid="{31B25D2E-7FCD-BC4A-948B-6E4C67219F72}"/>
     <hyperlink ref="K4" r:id="rId7" xr:uid="{0F950778-B761-374A-AF83-311F0B6581CF}"/>
@@ -1459,19 +1523,21 @@
     <hyperlink ref="K2" r:id="rId10" xr:uid="{F72405E6-10DE-5541-AAA9-6CE6B9DBDECE}"/>
     <hyperlink ref="K5" r:id="rId11" xr:uid="{8AB23E67-2D66-1142-B20B-6BFC3646BC7D}"/>
     <hyperlink ref="M5" r:id="rId12" xr:uid="{8772DFC9-4DFB-BF48-B50D-1136E2AD3525}"/>
-    <hyperlink ref="H15" r:id="rId13" xr:uid="{8F2A99B4-EF1A-E44F-A6E9-AF6F76A83C6A}"/>
-    <hyperlink ref="K15" r:id="rId14" xr:uid="{9C48DF42-9132-F74B-AEC6-9B18C373C7B8}"/>
-    <hyperlink ref="M15" r:id="rId15" xr:uid="{FB91E1BC-6602-C147-AC45-5CE751E349BC}"/>
-    <hyperlink ref="H16" r:id="rId16" xr:uid="{D969DFE3-72F2-FC46-AF63-BACD51F88111}"/>
-    <hyperlink ref="M16" r:id="rId17" xr:uid="{FD18C2C7-7B94-DD4B-BC68-D2F43975654B}"/>
-    <hyperlink ref="K16" r:id="rId18" xr:uid="{D42849F6-A732-7246-B17A-494F7AADFD90}"/>
-    <hyperlink ref="H11" r:id="rId19" xr:uid="{AE3EABA0-3E8F-4641-AC13-47FAE0871412}"/>
-    <hyperlink ref="M11" r:id="rId20" xr:uid="{CCA37CD9-E904-FF41-9A63-795B604A0EDA}"/>
+    <hyperlink ref="H16" r:id="rId13" xr:uid="{8F2A99B4-EF1A-E44F-A6E9-AF6F76A83C6A}"/>
+    <hyperlink ref="K16" r:id="rId14" xr:uid="{9C48DF42-9132-F74B-AEC6-9B18C373C7B8}"/>
+    <hyperlink ref="M16" r:id="rId15" xr:uid="{FB91E1BC-6602-C147-AC45-5CE751E349BC}"/>
+    <hyperlink ref="H17" r:id="rId16" xr:uid="{D969DFE3-72F2-FC46-AF63-BACD51F88111}"/>
+    <hyperlink ref="M17" r:id="rId17" xr:uid="{FD18C2C7-7B94-DD4B-BC68-D2F43975654B}"/>
+    <hyperlink ref="K17" r:id="rId18" xr:uid="{D42849F6-A732-7246-B17A-494F7AADFD90}"/>
+    <hyperlink ref="H12" r:id="rId19" xr:uid="{AE3EABA0-3E8F-4641-AC13-47FAE0871412}"/>
+    <hyperlink ref="M12" r:id="rId20" xr:uid="{CCA37CD9-E904-FF41-9A63-795B604A0EDA}"/>
     <hyperlink ref="H6" r:id="rId21" xr:uid="{8B2ABF59-6A09-D64E-A36C-82801EF3A6B8}"/>
     <hyperlink ref="M6" r:id="rId22" xr:uid="{A5ACDF0B-E628-7647-8966-0C1587EC2DB0}"/>
     <hyperlink ref="H7" r:id="rId23" xr:uid="{61BDCF0F-F4AD-784C-9848-84763C44F36B}"/>
     <hyperlink ref="M8" r:id="rId24" xr:uid="{58F61CBD-EA6F-1341-B53F-4365AFEC1F31}"/>
     <hyperlink ref="M9" r:id="rId25" xr:uid="{7D28E37E-5F6A-A947-A8C2-C1F4DEA478F1}"/>
+    <hyperlink ref="M11" r:id="rId26" xr:uid="{178CEAB6-CA45-CC48-A325-FF91097BC705}"/>
+    <hyperlink ref="H11" r:id="rId27" xr:uid="{26B174CB-695B-8044-9D25-6B310BB1B1E2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-2201-CommunityService.xlsx
+++ b/db/A7XLK-2201-CommunityService.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD7774F-7A0F-8241-BCC3-082C71C25DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3DACDE8-BB10-6F40-819C-D34E63987451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3980" yWindow="-19820" windowWidth="27920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
+    <workbookView xWindow="880" yWindow="-19820" windowWidth="27920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -1268,75 +1268,75 @@
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="16">
+    <row r="11" spans="1:14" ht="128">
       <c r="A11">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>98</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>122</v>
+        <v>97</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
       </c>
       <c r="G11" t="s">
-        <v>123</v>
+        <v>26</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="K11" s="1"/>
+        <v>27</v>
+      </c>
       <c r="L11" t="s">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="N11" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="128">
+        <v>34</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="16">
       <c r="A12">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="E12" t="s">
         <v>97</v>
       </c>
-      <c r="F12" t="s">
-        <v>25</v>
+      <c r="F12" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="G12" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>27</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="K12" s="1"/>
       <c r="L12" t="s">
-        <v>58</v>
+        <v>125</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>91</v>
+        <v>119</v>
+      </c>
+      <c r="N12" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1529,15 +1529,15 @@
     <hyperlink ref="H17" r:id="rId16" xr:uid="{D969DFE3-72F2-FC46-AF63-BACD51F88111}"/>
     <hyperlink ref="M17" r:id="rId17" xr:uid="{FD18C2C7-7B94-DD4B-BC68-D2F43975654B}"/>
     <hyperlink ref="K17" r:id="rId18" xr:uid="{D42849F6-A732-7246-B17A-494F7AADFD90}"/>
-    <hyperlink ref="H12" r:id="rId19" xr:uid="{AE3EABA0-3E8F-4641-AC13-47FAE0871412}"/>
-    <hyperlink ref="M12" r:id="rId20" xr:uid="{CCA37CD9-E904-FF41-9A63-795B604A0EDA}"/>
+    <hyperlink ref="H11" r:id="rId19" xr:uid="{AE3EABA0-3E8F-4641-AC13-47FAE0871412}"/>
+    <hyperlink ref="M11" r:id="rId20" xr:uid="{CCA37CD9-E904-FF41-9A63-795B604A0EDA}"/>
     <hyperlink ref="H6" r:id="rId21" xr:uid="{8B2ABF59-6A09-D64E-A36C-82801EF3A6B8}"/>
     <hyperlink ref="M6" r:id="rId22" xr:uid="{A5ACDF0B-E628-7647-8966-0C1587EC2DB0}"/>
     <hyperlink ref="H7" r:id="rId23" xr:uid="{61BDCF0F-F4AD-784C-9848-84763C44F36B}"/>
     <hyperlink ref="M8" r:id="rId24" xr:uid="{58F61CBD-EA6F-1341-B53F-4365AFEC1F31}"/>
     <hyperlink ref="M9" r:id="rId25" xr:uid="{7D28E37E-5F6A-A947-A8C2-C1F4DEA478F1}"/>
-    <hyperlink ref="M11" r:id="rId26" xr:uid="{178CEAB6-CA45-CC48-A325-FF91097BC705}"/>
-    <hyperlink ref="H11" r:id="rId27" xr:uid="{26B174CB-695B-8044-9D25-6B310BB1B1E2}"/>
+    <hyperlink ref="M12" r:id="rId26" xr:uid="{178CEAB6-CA45-CC48-A325-FF91097BC705}"/>
+    <hyperlink ref="H12" r:id="rId27" xr:uid="{26B174CB-695B-8044-9D25-6B310BB1B1E2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-2201-CommunityService.xlsx
+++ b/db/A7XLK-2201-CommunityService.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10520"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3DACDE8-BB10-6F40-819C-D34E63987451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84AA6C4-4640-9C40-A7EC-01935ED3881F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="880" yWindow="-19820" windowWidth="27920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
+    <workbookView xWindow="-940" yWindow="-19900" windowWidth="27920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="130">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -204,14 +204,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>03-327-8463, 0906-924-442</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>龜山賴生活 @523wlmiw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://www.facebook.com/20160101cg/</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -272,10 +264,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>龜山區長庚里長庚醫護新村 80 號B1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>龜山區萬壽路二段1050號</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -317,22 +305,6 @@
   </si>
   <si>
     <t>里長</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>長庚里</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>樂善里</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>文青里</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>文化里</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -538,6 +510,51 @@
   </si>
   <si>
     <t>fig/A7XLK-221-陳泓維.jpeg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>長庚里 里長及參選人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>樂善里 里長</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文青里 里長</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文化里 里長</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龜山區長庚里長庚醫護新村 167 號 7F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jjoorryy888@gmail.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0989-099-981, 03-327-8463</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經歷：第一屆 2014, 第二屆 2018 長庚里里長, &lt;br&gt;
+學歷：國立臺北護理健康大學 護理系, 慈濟大學 生理暨解剖醫學研究所</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://lin.ee/WwjxI19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>長庚里長參選人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳元信</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -924,7 +941,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A569E7E5-CF2A-7E44-B2C2-91A32E7499FF}">
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
@@ -953,7 +970,7 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -985,424 +1002,412 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2">
+        <v>207</v>
+      </c>
+      <c r="B2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="48">
+      <c r="A3">
         <v>203</v>
       </c>
-      <c r="B2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" t="s">
         <v>41</v>
       </c>
-      <c r="F2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="F3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L3" t="s">
+        <v>55</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L2" t="s">
-        <v>57</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3">
-        <v>204</v>
-      </c>
-      <c r="B3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" t="s">
-        <v>47</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L3" t="s">
-        <v>51</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>56</v>
+      <c r="N3" s="2" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L4" t="s">
         <v>49</v>
       </c>
-      <c r="G4" t="s">
-        <v>50</v>
-      </c>
-      <c r="K4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="L4" t="s">
-        <v>52</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="G5" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="L5" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6">
-        <v>311</v>
+        <v>206</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="G6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>19</v>
+        <v>61</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="L6" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>118</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>104</v>
+        <v>19</v>
       </c>
       <c r="L7" t="s">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="N7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="F8" t="s">
-        <v>113</v>
+        <v>29</v>
       </c>
       <c r="G8" t="s">
-        <v>114</v>
-      </c>
-      <c r="H8" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>97</v>
+      </c>
       <c r="L8" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="N8" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E9" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="F9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H9" s="1"/>
       <c r="L9" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="G10" t="s">
-        <v>50</v>
-      </c>
-      <c r="K10" s="1"/>
+        <v>102</v>
+      </c>
+      <c r="H10" s="1"/>
       <c r="L10" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="N10" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="128">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E11" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="G11" t="s">
-        <v>26</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>27</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="K11" s="1"/>
       <c r="L11" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="16">
+        <v>85</v>
+      </c>
+      <c r="N11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="128">
       <c r="A12">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>97</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>122</v>
+        <v>90</v>
+      </c>
+      <c r="F12" t="s">
+        <v>25</v>
       </c>
       <c r="G12" t="s">
-        <v>123</v>
+        <v>26</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="K12" s="1"/>
+        <v>27</v>
+      </c>
       <c r="L12" t="s">
-        <v>125</v>
+        <v>56</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="N12" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>34</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="16">
       <c r="A13">
-        <v>401</v>
+        <v>342</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="E13" t="s">
-        <v>96</v>
-      </c>
-      <c r="F13" t="s">
-        <v>60</v>
+        <v>90</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="G13" t="s">
-        <v>32</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K13" s="1"/>
       <c r="L13" t="s">
-        <v>39</v>
+        <v>118</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>40</v>
+        <v>112</v>
+      </c>
+      <c r="N13" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E14" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="F14" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="G14" t="s">
-        <v>22</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="L14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
@@ -1411,133 +1416,167 @@
         <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F15" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G15" t="s">
-        <v>30</v>
-      </c>
-      <c r="H15" t="s">
-        <v>69</v>
+        <v>22</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="144">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>81</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>75</v>
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" t="s">
+        <v>89</v>
+      </c>
+      <c r="F16" t="s">
+        <v>29</v>
       </c>
       <c r="G16" t="s">
-        <v>80</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>77</v>
+        <v>30</v>
+      </c>
+      <c r="H16" t="s">
+        <v>66</v>
       </c>
       <c r="L16" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="144">
       <c r="A17">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
       </c>
       <c r="C17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" t="s">
+        <v>73</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L17" t="s">
+        <v>71</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18">
+        <v>406</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" t="s">
+        <v>92</v>
+      </c>
+      <c r="F18" t="s">
+        <v>78</v>
+      </c>
+      <c r="G18" t="s">
+        <v>79</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L18" t="s">
+        <v>83</v>
+      </c>
+      <c r="M18" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D17" t="s">
-        <v>84</v>
-      </c>
-      <c r="E17" t="s">
-        <v>99</v>
-      </c>
-      <c r="F17" t="s">
-        <v>85</v>
-      </c>
-      <c r="G17" t="s">
-        <v>86</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="L17" t="s">
-        <v>90</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>88</v>
-      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N17">
-    <sortCondition ref="A2:A17"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:N18">
+    <sortCondition ref="A3:A18"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="H14" r:id="rId1" xr:uid="{54F4D35F-E2E2-C842-A43F-1D511AA423E2}"/>
-    <hyperlink ref="M14" r:id="rId2" xr:uid="{F2F6C49C-3706-8849-A592-2D557E4E0729}"/>
-    <hyperlink ref="M15" r:id="rId3" xr:uid="{70BEFD60-7B6E-D74B-BFFF-FC1C55DB4DC8}"/>
-    <hyperlink ref="M13" r:id="rId4" xr:uid="{3156EB90-5C6B-AE46-BC4D-1028A6B5CA40}"/>
-    <hyperlink ref="M2" r:id="rId5" xr:uid="{F79F65C5-A7F1-394D-841F-F98A2C79B07E}"/>
-    <hyperlink ref="M4" r:id="rId6" xr:uid="{31B25D2E-7FCD-BC4A-948B-6E4C67219F72}"/>
-    <hyperlink ref="K4" r:id="rId7" xr:uid="{0F950778-B761-374A-AF83-311F0B6581CF}"/>
-    <hyperlink ref="K3" r:id="rId8" xr:uid="{BA95A22C-8329-854A-B21A-08BE7A9E0A3D}"/>
-    <hyperlink ref="M3" r:id="rId9" xr:uid="{D0EE2661-AC9C-0841-8EFD-47FEA6E05264}"/>
-    <hyperlink ref="K2" r:id="rId10" xr:uid="{F72405E6-10DE-5541-AAA9-6CE6B9DBDECE}"/>
-    <hyperlink ref="K5" r:id="rId11" xr:uid="{8AB23E67-2D66-1142-B20B-6BFC3646BC7D}"/>
-    <hyperlink ref="M5" r:id="rId12" xr:uid="{8772DFC9-4DFB-BF48-B50D-1136E2AD3525}"/>
-    <hyperlink ref="H16" r:id="rId13" xr:uid="{8F2A99B4-EF1A-E44F-A6E9-AF6F76A83C6A}"/>
-    <hyperlink ref="K16" r:id="rId14" xr:uid="{9C48DF42-9132-F74B-AEC6-9B18C373C7B8}"/>
-    <hyperlink ref="M16" r:id="rId15" xr:uid="{FB91E1BC-6602-C147-AC45-5CE751E349BC}"/>
-    <hyperlink ref="H17" r:id="rId16" xr:uid="{D969DFE3-72F2-FC46-AF63-BACD51F88111}"/>
-    <hyperlink ref="M17" r:id="rId17" xr:uid="{FD18C2C7-7B94-DD4B-BC68-D2F43975654B}"/>
-    <hyperlink ref="K17" r:id="rId18" xr:uid="{D42849F6-A732-7246-B17A-494F7AADFD90}"/>
-    <hyperlink ref="H11" r:id="rId19" xr:uid="{AE3EABA0-3E8F-4641-AC13-47FAE0871412}"/>
-    <hyperlink ref="M11" r:id="rId20" xr:uid="{CCA37CD9-E904-FF41-9A63-795B604A0EDA}"/>
-    <hyperlink ref="H6" r:id="rId21" xr:uid="{8B2ABF59-6A09-D64E-A36C-82801EF3A6B8}"/>
-    <hyperlink ref="M6" r:id="rId22" xr:uid="{A5ACDF0B-E628-7647-8966-0C1587EC2DB0}"/>
-    <hyperlink ref="H7" r:id="rId23" xr:uid="{61BDCF0F-F4AD-784C-9848-84763C44F36B}"/>
-    <hyperlink ref="M8" r:id="rId24" xr:uid="{58F61CBD-EA6F-1341-B53F-4365AFEC1F31}"/>
-    <hyperlink ref="M9" r:id="rId25" xr:uid="{7D28E37E-5F6A-A947-A8C2-C1F4DEA478F1}"/>
-    <hyperlink ref="M12" r:id="rId26" xr:uid="{178CEAB6-CA45-CC48-A325-FF91097BC705}"/>
-    <hyperlink ref="H12" r:id="rId27" xr:uid="{26B174CB-695B-8044-9D25-6B310BB1B1E2}"/>
+    <hyperlink ref="H15" r:id="rId1" xr:uid="{54F4D35F-E2E2-C842-A43F-1D511AA423E2}"/>
+    <hyperlink ref="M15" r:id="rId2" xr:uid="{F2F6C49C-3706-8849-A592-2D557E4E0729}"/>
+    <hyperlink ref="M16" r:id="rId3" xr:uid="{70BEFD60-7B6E-D74B-BFFF-FC1C55DB4DC8}"/>
+    <hyperlink ref="M14" r:id="rId4" xr:uid="{3156EB90-5C6B-AE46-BC4D-1028A6B5CA40}"/>
+    <hyperlink ref="M3" r:id="rId5" xr:uid="{F79F65C5-A7F1-394D-841F-F98A2C79B07E}"/>
+    <hyperlink ref="M5" r:id="rId6" xr:uid="{31B25D2E-7FCD-BC4A-948B-6E4C67219F72}"/>
+    <hyperlink ref="K5" r:id="rId7" xr:uid="{0F950778-B761-374A-AF83-311F0B6581CF}"/>
+    <hyperlink ref="K4" r:id="rId8" xr:uid="{BA95A22C-8329-854A-B21A-08BE7A9E0A3D}"/>
+    <hyperlink ref="M4" r:id="rId9" xr:uid="{D0EE2661-AC9C-0841-8EFD-47FEA6E05264}"/>
+    <hyperlink ref="K3" r:id="rId10" xr:uid="{F72405E6-10DE-5541-AAA9-6CE6B9DBDECE}"/>
+    <hyperlink ref="K6" r:id="rId11" xr:uid="{8AB23E67-2D66-1142-B20B-6BFC3646BC7D}"/>
+    <hyperlink ref="M6" r:id="rId12" xr:uid="{8772DFC9-4DFB-BF48-B50D-1136E2AD3525}"/>
+    <hyperlink ref="H17" r:id="rId13" xr:uid="{8F2A99B4-EF1A-E44F-A6E9-AF6F76A83C6A}"/>
+    <hyperlink ref="K17" r:id="rId14" xr:uid="{9C48DF42-9132-F74B-AEC6-9B18C373C7B8}"/>
+    <hyperlink ref="M17" r:id="rId15" xr:uid="{FB91E1BC-6602-C147-AC45-5CE751E349BC}"/>
+    <hyperlink ref="H18" r:id="rId16" xr:uid="{D969DFE3-72F2-FC46-AF63-BACD51F88111}"/>
+    <hyperlink ref="M18" r:id="rId17" xr:uid="{FD18C2C7-7B94-DD4B-BC68-D2F43975654B}"/>
+    <hyperlink ref="K18" r:id="rId18" xr:uid="{D42849F6-A732-7246-B17A-494F7AADFD90}"/>
+    <hyperlink ref="H12" r:id="rId19" xr:uid="{AE3EABA0-3E8F-4641-AC13-47FAE0871412}"/>
+    <hyperlink ref="M12" r:id="rId20" xr:uid="{CCA37CD9-E904-FF41-9A63-795B604A0EDA}"/>
+    <hyperlink ref="H7" r:id="rId21" xr:uid="{8B2ABF59-6A09-D64E-A36C-82801EF3A6B8}"/>
+    <hyperlink ref="M7" r:id="rId22" xr:uid="{A5ACDF0B-E628-7647-8966-0C1587EC2DB0}"/>
+    <hyperlink ref="H8" r:id="rId23" xr:uid="{61BDCF0F-F4AD-784C-9848-84763C44F36B}"/>
+    <hyperlink ref="M9" r:id="rId24" xr:uid="{58F61CBD-EA6F-1341-B53F-4365AFEC1F31}"/>
+    <hyperlink ref="M10" r:id="rId25" xr:uid="{7D28E37E-5F6A-A947-A8C2-C1F4DEA478F1}"/>
+    <hyperlink ref="M13" r:id="rId26" xr:uid="{178CEAB6-CA45-CC48-A325-FF91097BC705}"/>
+    <hyperlink ref="H13" r:id="rId27" xr:uid="{26B174CB-695B-8044-9D25-6B310BB1B1E2}"/>
+    <hyperlink ref="H3" r:id="rId28" xr:uid="{F0AAC563-4BC3-E142-BD7C-C0D1F92A1F89}"/>
+    <hyperlink ref="I3" r:id="rId29" xr:uid="{99F3C94F-8166-B846-BBD9-4E66EA14719C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-2201-CommunityService.xlsx
+++ b/db/A7XLK-2201-CommunityService.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84AA6C4-4640-9C40-A7EC-01935ED3881F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABB1366-EDC7-9D45-ABC6-520360E4D2DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-940" yWindow="-19900" windowWidth="27920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
+    <workbookView xWindow="-7580" yWindow="-20120" windowWidth="27920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -374,11 +374,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>空污反應管道: &lt;a href="https://docs.google.com/forms/d/e/1FAIpQLScCA0u53XJRjzfBpjv9Bz4JrYH7D6v5wTtPwyVG_Jni0LK7zA/viewform?fbclid=IwAR3zGTtgLnLm8Hb_T45jnBz9iP_FPes2r1h-Z4-JTZeEkMPWiKw-L1OIwhQ"&gt;空污報馬仔&lt;/a&gt; &lt;br&gt;
-向市民報告 &lt;a href="https://issuu.com/niuhsuting/docs/220325_"&gt;環保議員 除公害&lt;/a&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://www.tpp.org.tw/action/result_content.php?id=58</t>
   </si>
   <si>
@@ -555,6 +550,13 @@
   </si>
   <si>
     <t>陳元信</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>空污反應管道: &lt;a href="https://docs.google.com/forms/d/e/1FAIpQLScCA0u53XJRjzfBpjv9Bz4JrYH7D6v5wTtPwyVG_Jni0LK7zA/viewform?fbclid=IwAR3zGTtgLnLm8Hb_T45jnBz9iP_FPes2r1h-Z4-JTZeEkMPWiKw-L1OIwhQ"&gt;空污報馬仔&lt;/a&gt; &lt;br&gt;
+向市民報告: &lt;a href="https://issuu.com/niuhsuting/docs/220325_"&gt;環保議員 除公害&lt;/a&gt;&lt;br&gt;
+交通問題民意調查: &lt;a href="https://docs.google.com/forms/d/e/1FAIpQLScjQbfA5PVLczJ8ibua4oa9DUHicpARK_9Ehg_yKjeuJ6ZSVA/viewform"&gt;A7,A8社區公車路線調查&lt;/a&gt;&lt;br&gt;
+線上捐款: &lt;a href="https://niu2022.oen.tw/?fbclid=IwAR3USt6j4wUWANHyalrGZBAwN3YUTM09BiyzaYaldS3kQnTse2gomFyr-60"&gt;挺牛的糧草&lt;/a&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -970,7 +972,7 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -1008,10 +1010,10 @@
         <v>67</v>
       </c>
       <c r="C2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D2" t="s">
         <v>128</v>
-      </c>
-      <c r="D2" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="48">
@@ -1022,22 +1024,22 @@
         <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D3" t="s">
         <v>41</v>
       </c>
       <c r="F3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G3" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>58</v>
@@ -1049,7 +1051,7 @@
         <v>42</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1060,7 +1062,7 @@
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D4" t="s">
         <v>43</v>
@@ -1089,7 +1091,7 @@
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D5" t="s">
         <v>46</v>
@@ -1118,7 +1120,7 @@
         <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D6" t="s">
         <v>59</v>
@@ -1147,13 +1149,13 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
         <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
@@ -1168,7 +1170,7 @@
         <v>36</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1182,10 +1184,10 @@
         <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F8" t="s">
         <v>29</v>
@@ -1194,16 +1196,16 @@
         <v>30</v>
       </c>
       <c r="H8" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="L8" t="s">
         <v>97</v>
       </c>
-      <c r="L8" t="s">
-        <v>98</v>
-      </c>
       <c r="M8" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1217,26 +1219,26 @@
         <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F9" t="s">
+        <v>105</v>
+      </c>
+      <c r="G9" t="s">
         <v>106</v>
-      </c>
-      <c r="G9" t="s">
-        <v>107</v>
       </c>
       <c r="H9" s="1"/>
       <c r="L9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1250,26 +1252,26 @@
         <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F10" t="s">
+        <v>100</v>
+      </c>
+      <c r="G10" t="s">
         <v>101</v>
-      </c>
-      <c r="G10" t="s">
-        <v>102</v>
       </c>
       <c r="H10" s="1"/>
       <c r="L10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1286,7 +1288,7 @@
         <v>46</v>
       </c>
       <c r="E11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F11" t="s">
         <v>47</v>
@@ -1296,16 +1298,16 @@
       </c>
       <c r="K11" s="1"/>
       <c r="L11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N11" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="128">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="256">
       <c r="A12">
         <v>341</v>
       </c>
@@ -1313,13 +1315,13 @@
         <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
         <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F12" t="s">
         <v>25</v>
@@ -1337,7 +1339,7 @@
         <v>34</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>84</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="16">
@@ -1351,29 +1353,29 @@
         <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G13" t="s">
         <v>115</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1390,7 +1392,7 @@
         <v>31</v>
       </c>
       <c r="E14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F14" t="s">
         <v>57</v>
@@ -1419,7 +1421,7 @@
         <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F15" t="s">
         <v>21</v>
@@ -1451,7 +1453,7 @@
         <v>28</v>
       </c>
       <c r="E16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F16" t="s">
         <v>29</v>
@@ -1483,7 +1485,7 @@
         <v>75</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>68</v>
@@ -1521,7 +1523,7 @@
         <v>77</v>
       </c>
       <c r="E18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F18" t="s">
         <v>78</v>

--- a/db/A7XLK-2201-CommunityService.xlsx
+++ b/db/A7XLK-2201-CommunityService.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABB1366-EDC7-9D45-ABC6-520360E4D2DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE52B28-D216-E442-9264-A646F1F1E628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-7580" yWindow="-20120" windowWidth="27920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
+    <workbookView xWindow="-5080" yWindow="-19800" windowWidth="27920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -536,11 +536,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>經歷：第一屆 2014, 第二屆 2018 長庚里里長, &lt;br&gt;
-學歷：國立臺北護理健康大學 護理系, 慈濟大學 生理暨解剖醫學研究所</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://lin.ee/WwjxI19</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -557,6 +552,12 @@
 向市民報告: &lt;a href="https://issuu.com/niuhsuting/docs/220325_"&gt;環保議員 除公害&lt;/a&gt;&lt;br&gt;
 交通問題民意調查: &lt;a href="https://docs.google.com/forms/d/e/1FAIpQLScjQbfA5PVLczJ8ibua4oa9DUHicpARK_9Ehg_yKjeuJ6ZSVA/viewform"&gt;A7,A8社區公車路線調查&lt;/a&gt;&lt;br&gt;
 線上捐款: &lt;a href="https://niu2022.oen.tw/?fbclid=IwAR3USt6j4wUWANHyalrGZBAwN3YUTM09BiyzaYaldS3kQnTse2gomFyr-60"&gt;挺牛的糧草&lt;/a&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LINE VOOM: &lt;a href="https://linevoom.line.me/user/_dU-v516WcUkyct-DQOQ46ViiEjoMzLNxDXwiMUc?utm_medium=osx&amp;utm_source=desktop&amp;utm_campaign=OA_Profile"&gt;長庚里公佈欄&lt;/a&gt;&lt;br&gt;
+經歷：第一屆 2014, 第二屆 2018 長庚里里長, &lt;br&gt;
+學歷：國立臺北護理健康大學 護理系, 慈濟大學 生理暨解剖醫學研究所</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1010,13 +1011,13 @@
         <v>67</v>
       </c>
       <c r="C2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2" t="s">
         <v>127</v>
       </c>
-      <c r="D2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="48">
+    </row>
+    <row r="3" spans="1:14" ht="128">
       <c r="A3">
         <v>203</v>
       </c>
@@ -1039,7 +1040,7 @@
         <v>123</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>58</v>
@@ -1051,7 +1052,7 @@
         <v>42</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1339,7 +1340,7 @@
         <v>34</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="16">

--- a/db/A7XLK-2201-CommunityService.xlsx
+++ b/db/A7XLK-2201-CommunityService.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE52B28-D216-E442-9264-A646F1F1E628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE28193E-D73E-C543-B204-B74F4114B881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5080" yWindow="-19800" windowWidth="27920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
+    <workbookView xWindow="-4700" yWindow="-19540" windowWidth="27920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="136">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -558,6 +558,30 @@
     <t>LINE VOOM: &lt;a href="https://linevoom.line.me/user/_dU-v516WcUkyct-DQOQ46ViiEjoMzLNxDXwiMUc?utm_medium=osx&amp;utm_source=desktop&amp;utm_campaign=OA_Profile"&gt;長庚里公佈欄&lt;/a&gt;&lt;br&gt;
 經歷：第一屆 2014, 第二屆 2018 長庚里里長, &lt;br&gt;
 學歷：國立臺北護理健康大學 護理系, 慈濟大學 生理暨解剖醫學研究所</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林雅珏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-221-林雅珏.jpeg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=100083021732591</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=100083021732591</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>五年級中段班，生於新北市板橋區，2016年搬來桃園市龜山區文青里。
+捐血活動、環保志工、守望相助、文青里11鄰長等多樣身分轉移了她人生目標，致力於貢獻能力在鄰里服務工作上。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文青里 里長參選人</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -944,7 +968,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A569E7E5-CF2A-7E44-B2C2-91A32E7499FF}">
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
@@ -1017,201 +1041,192 @@
         <v>127</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="128">
+    <row r="3" spans="1:14" ht="80">
       <c r="A3">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" t="s">
-        <v>122</v>
-      </c>
-      <c r="G3" t="s">
-        <v>124</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="L3" t="s">
-        <v>55</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>42</v>
+        <v>131</v>
+      </c>
+      <c r="M3" t="s">
+        <v>132</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="128">
       <c r="A4">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>122</v>
       </c>
       <c r="G4" t="s">
-        <v>45</v>
+        <v>124</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L4" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>54</v>
+        <v>42</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="G6" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="L6" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7">
-        <v>311</v>
+        <v>206</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="G7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>19</v>
+        <v>61</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="L7" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>110</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
         <v>88</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="L8" t="s">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="N8" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -1220,31 +1235,33 @@
         <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F9" t="s">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c r="G9" t="s">
-        <v>106</v>
-      </c>
-      <c r="H9" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="L9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="N9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
@@ -1253,31 +1270,31 @@
         <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
         <v>91</v>
       </c>
       <c r="F10" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G10" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H10" s="1"/>
       <c r="L10" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="N10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -1286,163 +1303,164 @@
         <v>65</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F11" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="G11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K11" s="1"/>
+        <v>101</v>
+      </c>
+      <c r="H11" s="1"/>
       <c r="L11" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="N11" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="256">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="G12" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>27</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="K12" s="1"/>
       <c r="L12" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="16">
+        <v>84</v>
+      </c>
+      <c r="N12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="256">
       <c r="A13">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>24</v>
       </c>
       <c r="E13" t="s">
         <v>89</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>114</v>
+      <c r="F13" t="s">
+        <v>25</v>
       </c>
       <c r="G13" t="s">
-        <v>115</v>
+        <v>26</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="K13" s="1"/>
+        <v>27</v>
+      </c>
       <c r="L13" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="N13" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>34</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="16">
       <c r="A14">
-        <v>401</v>
+        <v>342</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>112</v>
       </c>
       <c r="E14" t="s">
-        <v>88</v>
-      </c>
-      <c r="F14" t="s">
-        <v>57</v>
+        <v>89</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="G14" t="s">
-        <v>32</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="K14" s="1"/>
       <c r="L14" t="s">
-        <v>39</v>
+        <v>117</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>40</v>
+        <v>111</v>
+      </c>
+      <c r="N14" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F15" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="G15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="L15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
@@ -1451,68 +1469,62 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F16" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G16" t="s">
-        <v>30</v>
-      </c>
-      <c r="H16" t="s">
-        <v>66</v>
+        <v>22</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="144">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>68</v>
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" t="s">
+        <v>88</v>
+      </c>
+      <c r="F17" t="s">
+        <v>29</v>
       </c>
       <c r="G17" t="s">
-        <v>73</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>70</v>
+        <v>30</v>
+      </c>
+      <c r="H17" t="s">
+        <v>66</v>
       </c>
       <c r="L17" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="144">
       <c r="A18">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
@@ -1520,66 +1532,105 @@
       <c r="C18" t="s">
         <v>74</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" t="s">
+        <v>73</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L18" t="s">
+        <v>71</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19">
+        <v>406</v>
+      </c>
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" t="s">
         <v>77</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E19" t="s">
         <v>91</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F19" t="s">
         <v>78</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G19" t="s">
         <v>79</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H19" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="K19" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="L18" t="s">
+      <c r="L19" t="s">
         <v>83</v>
       </c>
-      <c r="M18" s="1" t="s">
+      <c r="M19" s="1" t="s">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:N18">
-    <sortCondition ref="A3:A18"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:N19">
+    <sortCondition ref="A4:A19"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="H15" r:id="rId1" xr:uid="{54F4D35F-E2E2-C842-A43F-1D511AA423E2}"/>
-    <hyperlink ref="M15" r:id="rId2" xr:uid="{F2F6C49C-3706-8849-A592-2D557E4E0729}"/>
-    <hyperlink ref="M16" r:id="rId3" xr:uid="{70BEFD60-7B6E-D74B-BFFF-FC1C55DB4DC8}"/>
-    <hyperlink ref="M14" r:id="rId4" xr:uid="{3156EB90-5C6B-AE46-BC4D-1028A6B5CA40}"/>
-    <hyperlink ref="M3" r:id="rId5" xr:uid="{F79F65C5-A7F1-394D-841F-F98A2C79B07E}"/>
-    <hyperlink ref="M5" r:id="rId6" xr:uid="{31B25D2E-7FCD-BC4A-948B-6E4C67219F72}"/>
-    <hyperlink ref="K5" r:id="rId7" xr:uid="{0F950778-B761-374A-AF83-311F0B6581CF}"/>
-    <hyperlink ref="K4" r:id="rId8" xr:uid="{BA95A22C-8329-854A-B21A-08BE7A9E0A3D}"/>
-    <hyperlink ref="M4" r:id="rId9" xr:uid="{D0EE2661-AC9C-0841-8EFD-47FEA6E05264}"/>
-    <hyperlink ref="K3" r:id="rId10" xr:uid="{F72405E6-10DE-5541-AAA9-6CE6B9DBDECE}"/>
-    <hyperlink ref="K6" r:id="rId11" xr:uid="{8AB23E67-2D66-1142-B20B-6BFC3646BC7D}"/>
-    <hyperlink ref="M6" r:id="rId12" xr:uid="{8772DFC9-4DFB-BF48-B50D-1136E2AD3525}"/>
-    <hyperlink ref="H17" r:id="rId13" xr:uid="{8F2A99B4-EF1A-E44F-A6E9-AF6F76A83C6A}"/>
-    <hyperlink ref="K17" r:id="rId14" xr:uid="{9C48DF42-9132-F74B-AEC6-9B18C373C7B8}"/>
-    <hyperlink ref="M17" r:id="rId15" xr:uid="{FB91E1BC-6602-C147-AC45-5CE751E349BC}"/>
-    <hyperlink ref="H18" r:id="rId16" xr:uid="{D969DFE3-72F2-FC46-AF63-BACD51F88111}"/>
-    <hyperlink ref="M18" r:id="rId17" xr:uid="{FD18C2C7-7B94-DD4B-BC68-D2F43975654B}"/>
-    <hyperlink ref="K18" r:id="rId18" xr:uid="{D42849F6-A732-7246-B17A-494F7AADFD90}"/>
-    <hyperlink ref="H12" r:id="rId19" xr:uid="{AE3EABA0-3E8F-4641-AC13-47FAE0871412}"/>
-    <hyperlink ref="M12" r:id="rId20" xr:uid="{CCA37CD9-E904-FF41-9A63-795B604A0EDA}"/>
-    <hyperlink ref="H7" r:id="rId21" xr:uid="{8B2ABF59-6A09-D64E-A36C-82801EF3A6B8}"/>
-    <hyperlink ref="M7" r:id="rId22" xr:uid="{A5ACDF0B-E628-7647-8966-0C1587EC2DB0}"/>
-    <hyperlink ref="H8" r:id="rId23" xr:uid="{61BDCF0F-F4AD-784C-9848-84763C44F36B}"/>
-    <hyperlink ref="M9" r:id="rId24" xr:uid="{58F61CBD-EA6F-1341-B53F-4365AFEC1F31}"/>
-    <hyperlink ref="M10" r:id="rId25" xr:uid="{7D28E37E-5F6A-A947-A8C2-C1F4DEA478F1}"/>
-    <hyperlink ref="M13" r:id="rId26" xr:uid="{178CEAB6-CA45-CC48-A325-FF91097BC705}"/>
-    <hyperlink ref="H13" r:id="rId27" xr:uid="{26B174CB-695B-8044-9D25-6B310BB1B1E2}"/>
-    <hyperlink ref="H3" r:id="rId28" xr:uid="{F0AAC563-4BC3-E142-BD7C-C0D1F92A1F89}"/>
-    <hyperlink ref="I3" r:id="rId29" xr:uid="{99F3C94F-8166-B846-BBD9-4E66EA14719C}"/>
+    <hyperlink ref="H16" r:id="rId1" xr:uid="{54F4D35F-E2E2-C842-A43F-1D511AA423E2}"/>
+    <hyperlink ref="M16" r:id="rId2" xr:uid="{F2F6C49C-3706-8849-A592-2D557E4E0729}"/>
+    <hyperlink ref="M17" r:id="rId3" xr:uid="{70BEFD60-7B6E-D74B-BFFF-FC1C55DB4DC8}"/>
+    <hyperlink ref="M15" r:id="rId4" xr:uid="{3156EB90-5C6B-AE46-BC4D-1028A6B5CA40}"/>
+    <hyperlink ref="M4" r:id="rId5" xr:uid="{F79F65C5-A7F1-394D-841F-F98A2C79B07E}"/>
+    <hyperlink ref="M6" r:id="rId6" xr:uid="{31B25D2E-7FCD-BC4A-948B-6E4C67219F72}"/>
+    <hyperlink ref="K6" r:id="rId7" xr:uid="{0F950778-B761-374A-AF83-311F0B6581CF}"/>
+    <hyperlink ref="K5" r:id="rId8" xr:uid="{BA95A22C-8329-854A-B21A-08BE7A9E0A3D}"/>
+    <hyperlink ref="M5" r:id="rId9" xr:uid="{D0EE2661-AC9C-0841-8EFD-47FEA6E05264}"/>
+    <hyperlink ref="K4" r:id="rId10" xr:uid="{F72405E6-10DE-5541-AAA9-6CE6B9DBDECE}"/>
+    <hyperlink ref="K7" r:id="rId11" xr:uid="{8AB23E67-2D66-1142-B20B-6BFC3646BC7D}"/>
+    <hyperlink ref="M7" r:id="rId12" xr:uid="{8772DFC9-4DFB-BF48-B50D-1136E2AD3525}"/>
+    <hyperlink ref="H18" r:id="rId13" xr:uid="{8F2A99B4-EF1A-E44F-A6E9-AF6F76A83C6A}"/>
+    <hyperlink ref="K18" r:id="rId14" xr:uid="{9C48DF42-9132-F74B-AEC6-9B18C373C7B8}"/>
+    <hyperlink ref="M18" r:id="rId15" xr:uid="{FB91E1BC-6602-C147-AC45-5CE751E349BC}"/>
+    <hyperlink ref="H19" r:id="rId16" xr:uid="{D969DFE3-72F2-FC46-AF63-BACD51F88111}"/>
+    <hyperlink ref="M19" r:id="rId17" xr:uid="{FD18C2C7-7B94-DD4B-BC68-D2F43975654B}"/>
+    <hyperlink ref="K19" r:id="rId18" xr:uid="{D42849F6-A732-7246-B17A-494F7AADFD90}"/>
+    <hyperlink ref="H13" r:id="rId19" xr:uid="{AE3EABA0-3E8F-4641-AC13-47FAE0871412}"/>
+    <hyperlink ref="M13" r:id="rId20" xr:uid="{CCA37CD9-E904-FF41-9A63-795B604A0EDA}"/>
+    <hyperlink ref="H8" r:id="rId21" xr:uid="{8B2ABF59-6A09-D64E-A36C-82801EF3A6B8}"/>
+    <hyperlink ref="M8" r:id="rId22" xr:uid="{A5ACDF0B-E628-7647-8966-0C1587EC2DB0}"/>
+    <hyperlink ref="H9" r:id="rId23" xr:uid="{61BDCF0F-F4AD-784C-9848-84763C44F36B}"/>
+    <hyperlink ref="M10" r:id="rId24" xr:uid="{58F61CBD-EA6F-1341-B53F-4365AFEC1F31}"/>
+    <hyperlink ref="M11" r:id="rId25" xr:uid="{7D28E37E-5F6A-A947-A8C2-C1F4DEA478F1}"/>
+    <hyperlink ref="M14" r:id="rId26" xr:uid="{178CEAB6-CA45-CC48-A325-FF91097BC705}"/>
+    <hyperlink ref="H14" r:id="rId27" xr:uid="{26B174CB-695B-8044-9D25-6B310BB1B1E2}"/>
+    <hyperlink ref="H4" r:id="rId28" xr:uid="{F0AAC563-4BC3-E142-BD7C-C0D1F92A1F89}"/>
+    <hyperlink ref="I4" r:id="rId29" xr:uid="{99F3C94F-8166-B846-BBD9-4E66EA14719C}"/>
+    <hyperlink ref="K3" r:id="rId30" xr:uid="{AE4F9FDA-6673-FD4A-8D4F-651D450123D8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
